--- a/docs/links/blank.xlsx
+++ b/docs/links/blank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bbell\Desktop\biolutoxR_package\biolutoxR_website\links\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B46AE75A-1899-47D9-A56B-123473A98D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637D27A9-1545-4AD1-A9B1-00E0E71D3E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -267,20 +267,20 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1109,104 +1109,104 @@
       <c r="X2" s="11"/>
     </row>
     <row r="3" spans="2:39" x14ac:dyDescent="0.3">
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13" t="s">
+      <c r="I3" s="10"/>
+      <c r="J3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="L3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="M3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="N3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="O3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="P3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13" t="s">
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="S3" s="13" t="s">
+      <c r="S3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="T3" s="13" t="s">
+      <c r="T3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="U3" s="13" t="s">
+      <c r="U3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="V3" s="13" t="s">
+      <c r="V3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="W3" s="13" t="s">
+      <c r="W3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="X3" s="13" t="s">
+      <c r="X3" s="10" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="2:39" x14ac:dyDescent="0.3">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="J5" s="10" t="s">
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="J5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="R5" s="10" t="s">
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="R5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="S5" s="10"/>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
-      <c r="W5" s="10"/>
-      <c r="X5" s="10"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
+      <c r="X5" s="13"/>
       <c r="Z5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA5" s="12" t="s">
+      <c r="AA5" s="14" t="s">
         <v>29</v>
       </c>
       <c r="AD5" s="11" t="s">
@@ -1216,13 +1216,13 @@
       <c r="AF5" s="11"/>
       <c r="AG5" s="11"/>
       <c r="AH5" s="11"/>
-      <c r="AI5" s="14" t="s">
+      <c r="AI5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AJ5" s="14"/>
-      <c r="AK5" s="14"/>
-      <c r="AL5" s="14"/>
-      <c r="AM5" s="14"/>
+      <c r="AJ5" s="12"/>
+      <c r="AK5" s="12"/>
+      <c r="AL5" s="12"/>
+      <c r="AM5" s="12"/>
     </row>
     <row r="6" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
@@ -1285,14 +1285,14 @@
       <c r="Z6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA6" s="12"/>
-      <c r="AI6" s="14" t="s">
+      <c r="AA6" s="14"/>
+      <c r="AI6" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AJ6" s="14"/>
-      <c r="AK6" s="14"/>
-      <c r="AL6" s="14"/>
-      <c r="AM6" s="14"/>
+      <c r="AJ6" s="12"/>
+      <c r="AK6" s="12"/>
+      <c r="AL6" s="12"/>
+      <c r="AM6" s="12"/>
     </row>
     <row r="7" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B7" s="9" t="s">
@@ -1325,14 +1325,14 @@
       <c r="Z7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA7" s="12"/>
-      <c r="AI7" s="14" t="s">
+      <c r="AA7" s="14"/>
+      <c r="AI7" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AJ7" s="14"/>
-      <c r="AK7" s="14"/>
-      <c r="AL7" s="14"/>
-      <c r="AM7" s="14"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="12"/>
+      <c r="AM7" s="12"/>
     </row>
     <row r="8" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B8" s="9" t="s">
@@ -1365,14 +1365,14 @@
       <c r="Z8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA8" s="12"/>
-      <c r="AI8" s="14" t="s">
+      <c r="AA8" s="14"/>
+      <c r="AI8" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AJ8" s="14"/>
-      <c r="AK8" s="14"/>
-      <c r="AL8" s="14"/>
-      <c r="AM8" s="14"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
     </row>
     <row r="9" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B9" s="9" t="s">
@@ -1405,14 +1405,14 @@
       <c r="Z9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA9" s="12"/>
-      <c r="AI9" s="14" t="s">
+      <c r="AA9" s="14"/>
+      <c r="AI9" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AJ9" s="14"/>
-      <c r="AK9" s="14"/>
-      <c r="AL9" s="14"/>
-      <c r="AM9" s="14"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
     </row>
     <row r="10" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B10" s="9" t="s">
@@ -1445,7 +1445,7 @@
       <c r="Z10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA10" s="12"/>
+      <c r="AA10" s="14"/>
     </row>
     <row r="11" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B11" s="9" t="s">
@@ -1478,46 +1478,46 @@
       <c r="Z11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA11" s="12"/>
+      <c r="AA11" s="14"/>
     </row>
     <row r="12" spans="2:39" x14ac:dyDescent="0.3">
       <c r="Z12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA12" s="12"/>
+      <c r="AA12" s="14"/>
     </row>
     <row r="13" spans="2:39" x14ac:dyDescent="0.3">
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="J13" s="10" t="s">
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="J13" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="R13" s="10" t="s">
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="R13" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="10"/>
+      <c r="S13" s="13"/>
+      <c r="T13" s="13"/>
+      <c r="U13" s="13"/>
+      <c r="V13" s="13"/>
+      <c r="W13" s="13"/>
+      <c r="X13" s="13"/>
       <c r="Z13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA13" s="12"/>
+      <c r="AA13" s="14"/>
     </row>
     <row r="14" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B14" s="8"/>
@@ -1580,7 +1580,7 @@
       <c r="Z14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA14" s="12"/>
+      <c r="AA14" s="14"/>
       <c r="AI14" s="11"/>
       <c r="AJ14" s="11"/>
       <c r="AK14" s="11"/>
@@ -1618,7 +1618,7 @@
       <c r="Z15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA15" s="12"/>
+      <c r="AA15" s="14"/>
       <c r="AD15" s="11" t="s">
         <v>32</v>
       </c>
@@ -1626,13 +1626,13 @@
       <c r="AF15" s="11"/>
       <c r="AG15" s="11"/>
       <c r="AH15" s="11"/>
-      <c r="AI15" s="14" t="s">
+      <c r="AI15" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AJ15" s="14"/>
-      <c r="AK15" s="14"/>
-      <c r="AL15" s="14"/>
-      <c r="AM15" s="14"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
     </row>
     <row r="16" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B16" s="9" t="s">
@@ -1665,14 +1665,14 @@
       <c r="Z16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA16" s="12"/>
-      <c r="AI16" s="14" t="s">
+      <c r="AA16" s="14"/>
+      <c r="AI16" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AJ16" s="14"/>
-      <c r="AK16" s="14"/>
-      <c r="AL16" s="14"/>
-      <c r="AM16" s="14"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
     </row>
     <row r="17" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B17" s="9" t="s">
@@ -1705,14 +1705,14 @@
       <c r="Z17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA17" s="12"/>
-      <c r="AI17" s="14" t="s">
+      <c r="AA17" s="14"/>
+      <c r="AI17" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AJ17" s="14"/>
-      <c r="AK17" s="14"/>
-      <c r="AL17" s="14"/>
-      <c r="AM17" s="14"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
     </row>
     <row r="18" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B18" s="9" t="s">
@@ -1745,14 +1745,14 @@
       <c r="Z18" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA18" s="12"/>
-      <c r="AI18" s="14" t="s">
+      <c r="AA18" s="14"/>
+      <c r="AI18" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AJ18" s="14"/>
-      <c r="AK18" s="14"/>
-      <c r="AL18" s="14"/>
-      <c r="AM18" s="14"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
     </row>
     <row r="19" spans="2:39" x14ac:dyDescent="0.3">
       <c r="B19" s="9" t="s">
@@ -1785,20 +1785,20 @@
       <c r="Z19" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA19" s="12"/>
-      <c r="AI19" s="14" t="s">
+      <c r="AA19" s="14"/>
+      <c r="AI19" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AJ19" s="14"/>
-      <c r="AK19" s="14"/>
-      <c r="AL19" s="14"/>
-      <c r="AM19" s="14"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
     </row>
     <row r="20" spans="2:39" x14ac:dyDescent="0.3">
       <c r="Z20" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA20" s="12"/>
+      <c r="AA20" s="14"/>
       <c r="AI20" s="11"/>
       <c r="AJ20" s="11"/>
       <c r="AK20" s="11"/>
@@ -1806,37 +1806,37 @@
       <c r="AM20" s="11"/>
     </row>
     <row r="21" spans="2:39" x14ac:dyDescent="0.3">
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="J21" s="10" t="s">
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="J21" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="10"/>
-      <c r="R21" s="10" t="s">
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="R21" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="S21" s="10"/>
-      <c r="T21" s="10"/>
-      <c r="U21" s="10"/>
-      <c r="V21" s="10"/>
-      <c r="W21" s="10"/>
-      <c r="X21" s="10"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="13"/>
+      <c r="U21" s="13"/>
+      <c r="V21" s="13"/>
+      <c r="W21" s="13"/>
+      <c r="X21" s="13"/>
       <c r="Z21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA21" s="12"/>
+      <c r="AA21" s="14"/>
       <c r="AI21" s="11"/>
       <c r="AJ21" s="11"/>
       <c r="AK21" s="11"/>
@@ -1904,7 +1904,7 @@
       <c r="Z22" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA22" s="12"/>
+      <c r="AA22" s="14"/>
       <c r="AI22" s="11"/>
       <c r="AJ22" s="11"/>
       <c r="AK22" s="11"/>
@@ -1942,7 +1942,7 @@
       <c r="Z23" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA23" s="12"/>
+      <c r="AA23" s="14"/>
       <c r="AI23" s="11"/>
       <c r="AJ23" s="11"/>
       <c r="AK23" s="11"/>
@@ -1980,7 +1980,7 @@
       <c r="Z24" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA24" s="12"/>
+      <c r="AA24" s="14"/>
       <c r="AI24" s="11"/>
       <c r="AJ24" s="11"/>
       <c r="AK24" s="11"/>
@@ -2018,7 +2018,7 @@
       <c r="Z25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA25" s="12"/>
+      <c r="AA25" s="14"/>
       <c r="AI25" s="11"/>
       <c r="AJ25" s="11"/>
       <c r="AK25" s="11"/>
@@ -2056,7 +2056,7 @@
       <c r="Z26" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA26" s="12"/>
+      <c r="AA26" s="14"/>
       <c r="AI26" s="11"/>
       <c r="AJ26" s="11"/>
       <c r="AK26" s="11"/>
@@ -2100,7 +2100,7 @@
       <c r="Z27" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AA27" s="12"/>
+      <c r="AA27" s="14"/>
     </row>
     <row r="28" spans="2:39" x14ac:dyDescent="0.3">
       <c r="W28" s="3" t="s">
@@ -2123,27 +2123,6 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="U30:Y30"/>
-    <mergeCell ref="AI22:AM22"/>
-    <mergeCell ref="AI23:AM23"/>
-    <mergeCell ref="AI24:AM24"/>
-    <mergeCell ref="AI25:AM25"/>
-    <mergeCell ref="AI26:AM26"/>
-    <mergeCell ref="AD15:AH15"/>
-    <mergeCell ref="AI20:AM20"/>
-    <mergeCell ref="AI21:AM21"/>
-    <mergeCell ref="AI16:AM16"/>
-    <mergeCell ref="AI17:AM17"/>
-    <mergeCell ref="AI18:AM18"/>
-    <mergeCell ref="AI19:AM19"/>
-    <mergeCell ref="AI14:AM14"/>
-    <mergeCell ref="AD5:AH5"/>
-    <mergeCell ref="AI5:AM5"/>
-    <mergeCell ref="AI6:AM6"/>
-    <mergeCell ref="AI7:AM7"/>
-    <mergeCell ref="AI8:AM8"/>
-    <mergeCell ref="AI15:AM15"/>
-    <mergeCell ref="AI9:AM9"/>
     <mergeCell ref="R5:X5"/>
     <mergeCell ref="R13:X13"/>
     <mergeCell ref="R21:X21"/>
@@ -2157,6 +2136,27 @@
     <mergeCell ref="J5:P5"/>
     <mergeCell ref="J13:P13"/>
     <mergeCell ref="J21:P21"/>
+    <mergeCell ref="AI14:AM14"/>
+    <mergeCell ref="AD5:AH5"/>
+    <mergeCell ref="AI5:AM5"/>
+    <mergeCell ref="AI6:AM6"/>
+    <mergeCell ref="AI7:AM7"/>
+    <mergeCell ref="AI8:AM8"/>
+    <mergeCell ref="AI9:AM9"/>
+    <mergeCell ref="AD15:AH15"/>
+    <mergeCell ref="AI20:AM20"/>
+    <mergeCell ref="AI21:AM21"/>
+    <mergeCell ref="AI16:AM16"/>
+    <mergeCell ref="AI17:AM17"/>
+    <mergeCell ref="AI18:AM18"/>
+    <mergeCell ref="AI19:AM19"/>
+    <mergeCell ref="AI15:AM15"/>
+    <mergeCell ref="U30:Y30"/>
+    <mergeCell ref="AI22:AM22"/>
+    <mergeCell ref="AI23:AM23"/>
+    <mergeCell ref="AI24:AM24"/>
+    <mergeCell ref="AI25:AM25"/>
+    <mergeCell ref="AI26:AM26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
